--- a/serial_template_TRK-20261011-0001.xlsx
+++ b/serial_template_TRK-20261011-0001.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\mdi-jurnal-app-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\mdi-jurnal-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A05308-29C1-45C9-AC0A-C4476A7614B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A8DDB1-A850-4A35-9DBA-5C5A01B621EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="56">
   <si>
     <t>sku</t>
   </si>
@@ -106,6 +106,123 @@
   </si>
   <si>
     <t>H660GM-A.011</t>
+  </si>
+  <si>
+    <t>H660GM-A.012</t>
+  </si>
+  <si>
+    <t>H660GM-A.013</t>
+  </si>
+  <si>
+    <t>H660GM-A.014</t>
+  </si>
+  <si>
+    <t>H660GM-A.015</t>
+  </si>
+  <si>
+    <t>H660GM-A.016</t>
+  </si>
+  <si>
+    <t>H660GM-A.017</t>
+  </si>
+  <si>
+    <t>H660GM-A.018</t>
+  </si>
+  <si>
+    <t>H660GM-A.019</t>
+  </si>
+  <si>
+    <t>H660GM-A.020</t>
+  </si>
+  <si>
+    <t>H660GM-A.021</t>
+  </si>
+  <si>
+    <t>H660GM-A.022</t>
+  </si>
+  <si>
+    <t>H660GM-A.023</t>
+  </si>
+  <si>
+    <t>H660GM-A.024</t>
+  </si>
+  <si>
+    <t>H660GM-A.025</t>
+  </si>
+  <si>
+    <t>H660GM-A.026</t>
+  </si>
+  <si>
+    <t>H660GM-A.027</t>
+  </si>
+  <si>
+    <t>H660GM-A.028</t>
+  </si>
+  <si>
+    <t>H660GM-A.029</t>
+  </si>
+  <si>
+    <t>H660GM-A.030</t>
+  </si>
+  <si>
+    <t>H660GM-A.031</t>
+  </si>
+  <si>
+    <t>H660GM-A.032</t>
+  </si>
+  <si>
+    <t>H660GM-A.033</t>
+  </si>
+  <si>
+    <t>H660GM-A.034</t>
+  </si>
+  <si>
+    <t>H660GM-A.035</t>
+  </si>
+  <si>
+    <t>H660GM-A.036</t>
+  </si>
+  <si>
+    <t>H660GM-A.037</t>
+  </si>
+  <si>
+    <t>H660GM-A.038</t>
+  </si>
+  <si>
+    <t>H660GM-A.039</t>
+  </si>
+  <si>
+    <t>H660GM-A.040</t>
+  </si>
+  <si>
+    <t>H660GM-A.041</t>
+  </si>
+  <si>
+    <t>H660GM-A.042</t>
+  </si>
+  <si>
+    <t>H660GM-A.043</t>
+  </si>
+  <si>
+    <t>H660GM-A.044</t>
+  </si>
+  <si>
+    <t>H660GM-A.045</t>
+  </si>
+  <si>
+    <t>H660GM-A.046</t>
+  </si>
+  <si>
+    <t>H660GM-A.047</t>
+  </si>
+  <si>
+    <t>H660GM-A.048</t>
+  </si>
+  <si>
+    <t>H660GM-A.049</t>
+  </si>
+  <si>
+    <t>H660GM-A.050</t>
   </si>
 </sst>
 </file>
@@ -462,7 +579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -639,6 +756,552 @@
         <v>16</v>
       </c>
     </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" t="s">
+        <v>5</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" t="s">
+        <v>5</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51" t="s">
+        <v>5</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
